--- a/光伏配储项目/电价数据/2026/榄州站.xlsx
+++ b/光伏配储项目/电价数据/2026/榄州站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5103799999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8220599999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6126</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.63337</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.52343</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.50958</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43751</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45433</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41993</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40878</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40205</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42303</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41247</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42065</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44393</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.2469</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12506</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10158</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11437</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.12603</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.11973</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.20541</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.25457</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.19613</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09089</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.16024</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.06738</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.21534</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24226</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.47906</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23231</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.12954</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.02744</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.26202</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.44191</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27844</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.54347</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.45673</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.20166</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.5726599999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.7815800000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.48182</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.54734</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.3395</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.44535</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.68226</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.5497000000000001</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.51383</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57717</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.46974</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6285700000000001</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8178099999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.65176</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.63789</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.78104</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.07907</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.46131</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6832999999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.57633</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.7794099999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.58526</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.57662</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.64777</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6197699999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47632</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41598</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42564</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70336</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.45896</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.74449</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.27801</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.78831</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52624</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51881</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50519</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50988</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48928</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46995</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50003</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59551</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.6874600000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42992</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.41992</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5188400000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.27843</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06188</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.63093</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.64258</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.62191</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.62325</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.57277</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.5585</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.54806</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.72248</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.35805</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.40676</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.82148</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.32013</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.51278</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.13649</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.59288</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.60445</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.5061600000000001</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.70941</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.62321</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.48287</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.50817</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.43407</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.60136</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.73146</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5941900000000001</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6988300000000001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.75579</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7328</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.60248</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.5472400000000001</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.74534</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.5547000000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.67579</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.04615</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.56559</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.71615</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.74099</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.50525</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4981</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.56008</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.56008</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.38307</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33456</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5059</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1.30131</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.13308</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.42041</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.44889</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.75859</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.43014</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.52207</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.4031</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47383</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.51964</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.5136000000000001</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.44385</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.40096</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>1.29599</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.38925</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.21287</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26756</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47756</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.4519</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.52443</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48899</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.42168</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16597</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27812</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28461</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.39253</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.39853</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.50783</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43112</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.39714</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.55215</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6296799999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.6716299999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.48651</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.51422</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.41922</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.46415</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.44743</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.46811</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.45423</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.41062</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.4343</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40278</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3424</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40213</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45821</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41137</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.27038</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.6469400000000001</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.5855900000000001</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.77475</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5968600000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.62341</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.79089</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.62612</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.19901</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.08823</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.43361</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.60094</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.02476</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06897</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.26902</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.27582</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.26703</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.25163</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.22426</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.28594</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.13685</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28741</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.59704</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46794</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.45491</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.45905</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.41957</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29924</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29628</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27923</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26034</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.20399</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04491</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.19815</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.22847</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04454</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04679</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.12353</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04747</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03395</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04688000000000001</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04701</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04202</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.0414</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04126</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.0416</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04156</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04047</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04204</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04516</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04142</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04166</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04275</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04784</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21866</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04644</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05264</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.02061</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.04135</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.22843</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.25223</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46757</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35093</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.85864</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44642</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10254</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04363</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0469</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.0454</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04609000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04546</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.0438</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03956</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04331</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10428</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00141</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04227</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04321</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04376</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04562</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04543999999999999</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04311</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04535</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04321</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04237</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04491</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04514</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04524</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04405</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04253</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04442</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.0445</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04993</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04726</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04765</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20009</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14298</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26908</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33569</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3179</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30159</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28826</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27119</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17257</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15881</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17113</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14787</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15877</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23643</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22673</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26904</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28597</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28073</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27161</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42788</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45447</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41791</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41479</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15642</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50771</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79095</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62207</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49802</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78106</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92048</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49462</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9160499999999999</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86799</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29929</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8928700000000001</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63262</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.1924</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8714299999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5456799999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33624</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03665</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53615</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79548</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53051</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77751</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78113</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8773300000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8762300000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49738</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40536</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45479</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21246</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8790399999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55115</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6272799999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53969</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4992799999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42493</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43814</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43383</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45085</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5867100000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42788</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5960700000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6024700000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.67065</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47205</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41892</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58121</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45218</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88162</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6348200000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.03801</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.01998</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8641799999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44314</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.64412</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.85472</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.55086</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45258</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35348</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9251900000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46739</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.42193</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47949</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40998</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5002799999999999</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26243</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19915</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19944</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27831</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25569</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38583</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43637</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44862</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42054</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40056</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59709</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89048</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.43403</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.22327</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7325700000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8345399999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.68288</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.60645</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.46384</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.46258</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.51836</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4521</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.44949</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.42491</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.42258</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.43423</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5185700000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.42258</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.44573</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.42174</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.44765</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4392200000000001</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.46372</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.40442</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.43415</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.44588</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.42258</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.42257</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40883</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.43431</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.45625</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.41595</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5158700000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40388</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.7601599999999999</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.28113</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.6074700000000001</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.7800499999999999</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25599</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.19906</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.6915</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.67083</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.84873</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26396</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26153</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.39023</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.41572</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57869</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.47375</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.82047</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.47968</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42227</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32409</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43051</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40507</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.75458</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.70525</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.71735</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.68168</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.55176</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.51327</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.21435</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.21423</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.52264</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.53865</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.6235700000000001</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.68424</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.76579</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.67118</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.53742</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.54003</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.56288</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.6207</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.6060800000000001</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.94096</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40757</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45874</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40619</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45333</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44874</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44799</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.45337</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.45352</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40801</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.40179</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34888</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.55852</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.48311</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.43403</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38691</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2732</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26433</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19928</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24843</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24116</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26831</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28755</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.26058</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24038</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.08545</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>-0.01357</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.14181</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.10439</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.14004</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.363</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.40369</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.9026000000000001</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.89112</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.8635499999999999</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.8727</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.8680800000000001</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.86372</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.8615499999999999</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.8647899999999999</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.8647999999999999</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.85582</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.85746</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.8585</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.86409</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.85863</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.87574</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.77812</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.46348</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40367</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43502</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.47342</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.16058</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25023</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.54535</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.2736</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.2285</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.27122</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28393</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.50622</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.45625</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70372</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50919</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26087</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.2875</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.65379</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.8539500000000001</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>1.3504</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39412</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40902</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34958</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42292</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41496</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64679</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.82026</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.44213</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46604</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34014</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14251</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28573</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20028</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26087</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28011</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22223</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.27306</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28591</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28012</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14619</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.4377799999999999</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.76779</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5831799999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.24517</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6833400000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.18568</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.7091000000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44024</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47149</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40936</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47775</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36006</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.4901</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.51788</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47208</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.47861</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41812</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39412</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.4030899999999999</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40997</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41284</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42088</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41372</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41611</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42707</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.42112</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41711</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.46177</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45235</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.57636</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5166799999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.46202</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.28749</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44257</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.48835</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.45465</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.49035</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.47755</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5985</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43557</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.46235</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.42616</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42661</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6473099999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.17036</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29607</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42562</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44569</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.5059</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44691</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.52891</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.49844</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.5086499999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.6885399999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7145900000000001</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80952</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.57828</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.50768</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.77855</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62207</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.65326</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47697</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46929</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47761</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.45613</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.54806</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44159</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44897</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42269</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44013</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40659</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44703</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4065299999999999</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.22276</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40505</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46952</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46424</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11594</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18095</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.44217</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41663</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4301</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41777</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41491</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40898</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40822</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36553</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44507</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39668</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27765</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22773</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23059</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25043</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26287</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14002</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25305</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04327</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25126</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17036</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18314</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28295</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22905</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25015</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26605</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23256</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27563</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35024</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.27081</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17563</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21852</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.24299</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00082</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02379</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04921</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1.11974</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.99036</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03919</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04923</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01271</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0381</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03476</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.9524400000000001</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04701</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02373</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02434</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04926</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.13842</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04923</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04904</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04904</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03029</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04922</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04903</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04152</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18515</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20948</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.24588</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27323</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27491</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27331</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29448</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30175</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28949</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.42143</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29765</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.17691</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.63767</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.44254</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.20777</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.26923</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.26173</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.27193</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.24644</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.27535</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.26161</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.28483</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26982</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.25031</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.20432</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.69362</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.69438</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6992200000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.64442</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.19491</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.12182</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.25146</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.20874</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.15676</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.16136</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.23698</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.14586</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.05494</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.08823</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.13408</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04593</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.19552</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02124</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.15543</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.16331</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.17592</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.00256</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.13816</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.14764</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.14679</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.18028</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27843</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38828</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.43721</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32353</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.05193</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.55944</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.51989</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.41824</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.40594</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.42485</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.44267</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43319</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44607</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14128</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27785</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27017</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.44409</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32659</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.54944</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.52683</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.4866</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.43203</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26268</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.27793</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40433</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47312</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.48075</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.44673</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.4614</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42259</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.56797</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.52754</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41545</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.71485</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.48379</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41638</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.39574</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36454</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.43589</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.19997</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36179</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48082</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.49855</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.5246799999999999</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.41034</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.4606</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27364</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.48916</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.40952</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.45563</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.43703</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43205</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49597</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5605399999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.56096</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39514</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45162</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.52062</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.48972</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.52332</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.46574</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.51275</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.48826</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.44555</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7406200000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.53708</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5435399999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.42546</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36718</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26568</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.24491</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27724</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.28427</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.18042</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06956</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.19916</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.03664</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.1727</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.005900000000000001</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26358</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16716</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06220000000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05496</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07442</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17161</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08215</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.18164</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15665</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.17699</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.28986</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26432</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42298</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40742</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.42141</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41868</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.41381</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4193</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.19892</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36223</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8198200000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43304</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38691</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.28029</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.27301</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.26701</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11695</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01298</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01295</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01027</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03831</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.16797</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03315</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00578</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01871</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04547</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01726</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01122</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16255</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.27854</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04482999999999999</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.25056</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.17194</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.27133</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48798</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40735</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.53364</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.19141</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40543</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36525</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5612999999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.44592</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26926</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.24082</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14996</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21784</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.24176</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24623</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15921</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.02894</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04715999999999999</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04717</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04554</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04603</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04403</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04131</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08176</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02828</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06475</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.10063</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.18082</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.2081</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12678</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27443</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.2431</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.13006</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.06922</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.1559</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.12238</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.24512</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19657</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.25367</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.2585</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.21444</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.25705</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45176</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38309</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37505</v>
       </c>
     </row>
   </sheetData>
